--- a/lesson6-1/data/sensor_data.xlsx
+++ b/lesson6-1/data/sensor_data.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:47</t>
+          <t>2025-12-04 17:14:15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -465,27 +465,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:47</t>
+          <t>2025-12-04 17:14:15</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:47</t>
+          <t>2025-12-04 17:14:15</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:49</t>
+          <t>2025-12-04 17:14:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,27 +497,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:49</t>
+          <t>2025-12-04 17:14:17</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:49</t>
+          <t>2025-12-04 17:14:17</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>65.40000000000001</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:51</t>
+          <t>2025-12-04 17:14:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -529,27 +529,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:51</t>
+          <t>2025-12-04 17:14:19</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.3</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:51</t>
+          <t>2025-12-04 17:14:19</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:53</t>
+          <t>2025-12-04 17:14:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -561,27 +561,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:53</t>
+          <t>2025-12-04 17:14:21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.9</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:53</t>
+          <t>2025-12-04 17:14:21</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.7</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:55</t>
+          <t>2025-12-04 17:14:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -593,27 +593,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:55</t>
+          <t>2025-12-04 17:14:23</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.3</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:55</t>
+          <t>2025-12-04 17:14:23</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>62.7</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:57</t>
+          <t>2025-12-04 17:14:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -625,27 +625,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:57</t>
+          <t>2025-12-04 17:14:25</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.8</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:57</t>
+          <t>2025-12-04 17:14:25</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65.40000000000001</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:59</t>
+          <t>2025-12-04 17:14:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -657,27 +657,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:59</t>
+          <t>2025-12-04 17:14:27</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-04 17:13:59</t>
+          <t>2025-12-04 17:14:27</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53.7</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:01</t>
+          <t>2025-12-04 17:14:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -689,27 +689,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:01</t>
+          <t>2025-12-04 17:14:29</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:01</t>
+          <t>2025-12-04 17:14:29</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65.40000000000001</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:03</t>
+          <t>2025-12-04 17:14:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -721,27 +721,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:03</t>
+          <t>2025-12-04 17:14:31</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.9</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:03</t>
+          <t>2025-12-04 17:14:31</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56.2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:05</t>
+          <t>2025-12-04 17:14:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:05</t>
+          <t>2025-12-04 17:14:33</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:05</t>
+          <t>2025-12-04 17:14:33</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60.6</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:07</t>
+          <t>2025-12-04 17:14:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:07</t>
+          <t>2025-12-04 17:14:35</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>27.1</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:07</t>
+          <t>2025-12-04 17:14:35</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>59.1</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:09</t>
+          <t>2025-12-04 17:14:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:09</t>
+          <t>2025-12-04 17:14:37</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>29.3</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:09</t>
+          <t>2025-12-04 17:14:37</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>54.7</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:11</t>
+          <t>2025-12-04 17:14:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:11</t>
+          <t>2025-12-04 17:14:39</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24.6</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:11</t>
+          <t>2025-12-04 17:14:39</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>54.9</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:13</t>
+          <t>2025-12-04 17:14:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:13</t>
+          <t>2025-12-04 17:14:41</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25.4</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:13</t>
+          <t>2025-12-04 17:14:41</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>68.7</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:15</t>
+          <t>2025-12-04 17:14:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:15</t>
+          <t>2025-12-04 17:14:43</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>26.4</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:15</t>
+          <t>2025-12-04 17:14:43</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>68.09999999999999</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:17</t>
+          <t>2025-12-04 17:14:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:17</t>
+          <t>2025-12-04 17:14:45</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.3</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:17</t>
+          <t>2025-12-04 17:14:45</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>56.8</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:19</t>
+          <t>2025-12-04 17:14:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:19</t>
+          <t>2025-12-04 17:14:47</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:19</t>
+          <t>2025-12-04 17:14:47</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>55</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:21</t>
+          <t>2025-12-04 17:14:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:21</t>
+          <t>2025-12-04 17:14:49</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>26.7</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:21</t>
+          <t>2025-12-04 17:14:49</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>57.7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:23</t>
+          <t>2025-12-04 17:14:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:23</t>
+          <t>2025-12-04 17:14:51</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:23</t>
+          <t>2025-12-04 17:14:51</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>54.3</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:25</t>
+          <t>2025-12-04 17:14:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:25</t>
+          <t>2025-12-04 17:14:53</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27.8</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:25</t>
+          <t>2025-12-04 17:14:53</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>53.7</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:27</t>
+          <t>2025-12-04 17:14:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:27</t>
+          <t>2025-12-04 17:14:55</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:27</t>
+          <t>2025-12-04 17:14:55</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>58.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:29</t>
+          <t>2025-12-04 17:14:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:29</t>
+          <t>2025-12-04 17:14:57</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>25.4</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:29</t>
+          <t>2025-12-04 17:14:57</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>60</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:31</t>
+          <t>2025-12-04 17:14:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:31</t>
+          <t>2025-12-04 17:14:59</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>28.5</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:31</t>
+          <t>2025-12-04 17:14:59</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>67</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:33</t>
+          <t>2025-12-04 17:15:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1201,27 +1201,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:33</t>
+          <t>2025-12-04 17:15:01</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:33</t>
+          <t>2025-12-04 17:15:01</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>67.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:35</t>
+          <t>2025-12-04 17:15:03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1233,27 +1233,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:35</t>
+          <t>2025-12-04 17:15:03</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>29.6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:35</t>
+          <t>2025-12-04 17:15:03</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>60.3</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:37</t>
+          <t>2025-12-04 17:15:05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1265,27 +1265,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:37</t>
+          <t>2025-12-04 17:15:05</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>24.4</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:37</t>
+          <t>2025-12-04 17:15:05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>65.90000000000001</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:39</t>
+          <t>2025-12-04 17:15:07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1297,27 +1297,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:39</t>
+          <t>2025-12-04 17:15:07</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>26.5</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:39</t>
+          <t>2025-12-04 17:15:07</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>63.6</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:41</t>
+          <t>2025-12-04 17:15:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1329,27 +1329,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:41</t>
+          <t>2025-12-04 17:15:09</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>26.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:41</t>
+          <t>2025-12-04 17:15:09</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>51.8</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:43</t>
+          <t>2025-12-04 17:15:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1361,27 +1361,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:43</t>
+          <t>2025-12-04 17:15:11</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:43</t>
+          <t>2025-12-04 17:15:11</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>63.5</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:45</t>
+          <t>2025-12-04 17:15:13</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1393,27 +1393,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:45</t>
+          <t>2025-12-04 17:15:13</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>24.2</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:45</t>
+          <t>2025-12-04 17:15:13</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>65.2</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:47</t>
+          <t>2025-12-04 17:15:15</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1425,27 +1425,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:47</t>
+          <t>2025-12-04 17:15:15</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>24.8</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:47</t>
+          <t>2025-12-04 17:15:15</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>57.3</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:49</t>
+          <t>2025-12-04 17:15:17</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1457,27 +1457,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:49</t>
+          <t>2025-12-04 17:15:17</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:49</t>
+          <t>2025-12-04 17:15:17</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>53</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:51</t>
+          <t>2025-12-04 17:15:19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1489,27 +1489,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:51</t>
+          <t>2025-12-04 17:15:19</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>24.9</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:51</t>
+          <t>2025-12-04 17:15:19</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>57.2</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:53</t>
+          <t>2025-12-04 17:15:21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1521,27 +1521,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:53</t>
+          <t>2025-12-04 17:15:21</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:53</t>
+          <t>2025-12-04 17:15:21</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>62.2</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:55</t>
+          <t>2025-12-04 17:15:23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1553,27 +1553,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:55</t>
+          <t>2025-12-04 17:15:23</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>27.2</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:55</t>
+          <t>2025-12-04 17:15:23</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>52.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:57</t>
+          <t>2025-12-04 17:15:25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:57</t>
+          <t>2025-12-04 17:15:25</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -1595,17 +1595,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:57</t>
+          <t>2025-12-04 17:15:25</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>58.6</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:59</t>
+          <t>2025-12-04 17:15:27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -1617,27 +1617,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:59</t>
+          <t>2025-12-04 17:15:27</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>29.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-12-04 17:14:59</t>
+          <t>2025-12-04 17:15:27</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>63.9</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:01</t>
+          <t>2025-12-04 17:15:29</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -1649,27 +1649,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:01</t>
+          <t>2025-12-04 17:15:29</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>27.5</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:01</t>
+          <t>2025-12-04 17:15:29</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>65.09999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:03</t>
+          <t>2025-12-04 17:15:31</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -1681,27 +1681,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:03</t>
+          <t>2025-12-04 17:15:31</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:03</t>
+          <t>2025-12-04 17:15:31</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>65.59999999999999</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:05</t>
+          <t>2025-12-04 17:15:33</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -1713,27 +1713,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:05</t>
+          <t>2025-12-04 17:15:33</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:05</t>
+          <t>2025-12-04 17:15:33</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>52.4</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:07</t>
+          <t>2025-12-04 17:15:35</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1745,27 +1745,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:07</t>
+          <t>2025-12-04 17:15:35</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>25.1</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:07</t>
+          <t>2025-12-04 17:15:35</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>54.2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:09</t>
+          <t>2025-12-04 17:15:37</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -1777,27 +1777,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:09</t>
+          <t>2025-12-04 17:15:37</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>29.5</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:09</t>
+          <t>2025-12-04 17:15:37</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>68.59999999999999</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:11</t>
+          <t>2025-12-04 17:15:39</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -1809,27 +1809,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:11</t>
+          <t>2025-12-04 17:15:39</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>24.4</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:11</t>
+          <t>2025-12-04 17:15:39</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>69.7</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:13</t>
+          <t>2025-12-04 17:15:41</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -1841,27 +1841,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:13</t>
+          <t>2025-12-04 17:15:41</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>26.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:13</t>
+          <t>2025-12-04 17:15:41</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>50.3</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:15</t>
+          <t>2025-12-04 17:15:43</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -1873,27 +1873,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:15</t>
+          <t>2025-12-04 17:15:43</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:15</t>
+          <t>2025-12-04 17:15:43</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>51.3</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:17</t>
+          <t>2025-12-04 17:15:45</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -1905,27 +1905,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:17</t>
+          <t>2025-12-04 17:15:45</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>25.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:17</t>
+          <t>2025-12-04 17:15:45</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>54.9</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:19</t>
+          <t>2025-12-04 17:15:47</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -1937,27 +1937,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:19</t>
+          <t>2025-12-04 17:15:47</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:19</t>
+          <t>2025-12-04 17:15:47</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>56.2</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:21</t>
+          <t>2025-12-04 17:15:49</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -1969,27 +1969,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:21</t>
+          <t>2025-12-04 17:15:49</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>28.5</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:21</t>
+          <t>2025-12-04 17:15:49</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>50.1</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:23</t>
+          <t>2025-12-04 17:15:51</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2001,27 +2001,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:23</t>
+          <t>2025-12-04 17:15:51</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>28.5</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:23</t>
+          <t>2025-12-04 17:15:51</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>58</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:25</t>
+          <t>2025-12-04 17:15:53</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2033,27 +2033,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:25</t>
+          <t>2025-12-04 17:15:53</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>24.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:25</t>
+          <t>2025-12-04 17:15:53</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>60.4</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:27</t>
+          <t>2025-12-04 17:15:55</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2065,27 +2065,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:27</t>
+          <t>2025-12-04 17:15:55</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>24.8</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:27</t>
+          <t>2025-12-04 17:15:55</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>50.4</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:29</t>
+          <t>2025-12-04 17:15:57</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2097,27 +2097,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:29</t>
+          <t>2025-12-04 17:15:57</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>24.8</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:29</t>
+          <t>2025-12-04 17:15:57</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>63.7</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:31</t>
+          <t>2025-12-04 17:15:59</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2129,27 +2129,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:31</t>
+          <t>2025-12-04 17:15:59</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>29</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:31</t>
+          <t>2025-12-04 17:15:59</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>59.7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:33</t>
+          <t>2025-12-04 17:16:01</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2161,27 +2161,27 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:33</t>
+          <t>2025-12-04 17:16:01</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>26.8</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:33</t>
+          <t>2025-12-04 17:16:01</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>61.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:35</t>
+          <t>2025-12-04 17:16:03</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2193,27 +2193,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:35</t>
+          <t>2025-12-04 17:16:03</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>27.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:35</t>
+          <t>2025-12-04 17:16:03</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>54</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:37</t>
+          <t>2025-12-04 17:16:05</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2225,27 +2225,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:37</t>
+          <t>2025-12-04 17:16:05</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:37</t>
+          <t>2025-12-04 17:16:05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>54.1</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:39</t>
+          <t>2025-12-04 17:16:07</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2257,27 +2257,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:39</t>
+          <t>2025-12-04 17:16:07</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:39</t>
+          <t>2025-12-04 17:16:07</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>68.40000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:41</t>
+          <t>2025-12-04 17:16:09</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -2289,27 +2289,27 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:41</t>
+          <t>2025-12-04 17:16:09</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:41</t>
+          <t>2025-12-04 17:16:09</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>57.6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:43</t>
+          <t>2025-12-04 17:16:11</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -2321,27 +2321,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:43</t>
+          <t>2025-12-04 17:16:11</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:43</t>
+          <t>2025-12-04 17:16:11</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>65.8</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:45</t>
+          <t>2025-12-04 17:16:13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -2353,27 +2353,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:45</t>
+          <t>2025-12-04 17:16:13</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>29.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:45</t>
+          <t>2025-12-04 17:16:13</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>56.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:47</t>
+          <t>2025-12-04 17:16:15</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -2385,27 +2385,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:47</t>
+          <t>2025-12-04 17:16:15</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>24.1</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:47</t>
+          <t>2025-12-04 17:16:15</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>66.09999999999999</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:49</t>
+          <t>2025-12-04 17:16:17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2417,27 +2417,27 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:49</t>
+          <t>2025-12-04 17:16:17</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>27.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:49</t>
+          <t>2025-12-04 17:16:17</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>64.40000000000001</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:51</t>
+          <t>2025-12-04 17:16:19</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -2449,27 +2449,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:51</t>
+          <t>2025-12-04 17:16:19</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>26.2</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:51</t>
+          <t>2025-12-04 17:16:19</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>69.3</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:53</t>
+          <t>2025-12-04 17:16:21</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -2481,27 +2481,27 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:53</t>
+          <t>2025-12-04 17:16:21</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:53</t>
+          <t>2025-12-04 17:16:21</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>67.3</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:55</t>
+          <t>2025-12-04 17:16:23</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -2513,27 +2513,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:55</t>
+          <t>2025-12-04 17:16:23</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>28.3</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:55</t>
+          <t>2025-12-04 17:16:23</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>58.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:57</t>
+          <t>2025-12-04 17:16:25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -2545,27 +2545,27 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:57</t>
+          <t>2025-12-04 17:16:25</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:57</t>
+          <t>2025-12-04 17:16:25</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>57.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:59</t>
+          <t>2025-12-04 17:16:27</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -2577,27 +2577,27 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:59</t>
+          <t>2025-12-04 17:16:27</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>26.1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-12-04 17:15:59</t>
+          <t>2025-12-04 17:16:27</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>59</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:01</t>
+          <t>2025-12-04 17:16:29</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -2609,27 +2609,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:01</t>
+          <t>2025-12-04 17:16:29</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>29.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:01</t>
+          <t>2025-12-04 17:16:29</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>53</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:03</t>
+          <t>2025-12-04 17:16:31</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -2641,27 +2641,27 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:03</t>
+          <t>2025-12-04 17:16:31</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>24.6</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:03</t>
+          <t>2025-12-04 17:16:31</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>65.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:05</t>
+          <t>2025-12-04 17:16:33</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2673,27 +2673,27 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:05</t>
+          <t>2025-12-04 17:16:33</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>26.4</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:05</t>
+          <t>2025-12-04 17:16:33</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>63.2</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:07</t>
+          <t>2025-12-04 17:16:35</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2705,27 +2705,27 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:07</t>
+          <t>2025-12-04 17:16:35</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:07</t>
+          <t>2025-12-04 17:16:35</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>66.7</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:09</t>
+          <t>2025-12-04 17:16:37</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -2737,27 +2737,27 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:09</t>
+          <t>2025-12-04 17:16:37</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>25.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:09</t>
+          <t>2025-12-04 17:16:37</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:11</t>
+          <t>2025-12-04 17:16:39</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -2769,27 +2769,27 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:11</t>
+          <t>2025-12-04 17:16:39</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>26.8</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:11</t>
+          <t>2025-12-04 17:16:39</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>55.7</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:13</t>
+          <t>2025-12-04 17:16:41</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -2801,27 +2801,27 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:13</t>
+          <t>2025-12-04 17:16:41</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>25.7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:13</t>
+          <t>2025-12-04 17:16:41</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>60</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:15</t>
+          <t>2025-12-04 17:16:43</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -2833,27 +2833,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:15</t>
+          <t>2025-12-04 17:16:43</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>26.6</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:15</t>
+          <t>2025-12-04 17:16:43</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>50.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:17</t>
+          <t>2025-12-04 17:16:45</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -2865,27 +2865,27 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:17</t>
+          <t>2025-12-04 17:16:45</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:17</t>
+          <t>2025-12-04 17:16:45</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>50.1</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:19</t>
+          <t>2025-12-04 17:16:47</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -2897,27 +2897,27 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:19</t>
+          <t>2025-12-04 17:16:47</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>29.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:19</t>
+          <t>2025-12-04 17:16:47</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>60.7</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:21</t>
+          <t>2025-12-04 17:16:49</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -2929,27 +2929,27 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:21</t>
+          <t>2025-12-04 17:16:49</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>29.5</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:21</t>
+          <t>2025-12-04 17:16:49</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:23</t>
+          <t>2025-12-04 17:16:51</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -2961,27 +2961,27 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:23</t>
+          <t>2025-12-04 17:16:51</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>24.6</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:23</t>
+          <t>2025-12-04 17:16:51</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>62.5</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:25</t>
+          <t>2025-12-04 17:16:53</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -2993,27 +2993,27 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:25</t>
+          <t>2025-12-04 17:16:53</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>25.2</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:25</t>
+          <t>2025-12-04 17:16:53</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>51.1</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:27</t>
+          <t>2025-12-04 17:16:55</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -3025,27 +3025,27 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:27</t>
+          <t>2025-12-04 17:16:55</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:27</t>
+          <t>2025-12-04 17:16:55</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>52.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:29</t>
+          <t>2025-12-04 17:16:57</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -3057,27 +3057,27 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:29</t>
+          <t>2025-12-04 17:16:57</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:29</t>
+          <t>2025-12-04 17:16:57</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>68.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:31</t>
+          <t>2025-12-04 17:16:59</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -3089,27 +3089,27 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:31</t>
+          <t>2025-12-04 17:16:59</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:31</t>
+          <t>2025-12-04 17:16:59</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>69</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:33</t>
+          <t>2025-12-04 17:17:01</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -3121,27 +3121,27 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:33</t>
+          <t>2025-12-04 17:17:01</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:33</t>
+          <t>2025-12-04 17:17:01</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>64.3</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:35</t>
+          <t>2025-12-04 17:17:03</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:35</t>
+          <t>2025-12-04 17:17:03</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -3163,17 +3163,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:35</t>
+          <t>2025-12-04 17:17:03</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>61.2</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:37</t>
+          <t>2025-12-04 17:17:05</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -3185,27 +3185,27 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:37</t>
+          <t>2025-12-04 17:17:05</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:37</t>
+          <t>2025-12-04 17:17:05</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>65</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:39</t>
+          <t>2025-12-04 18:18:53</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -3217,27 +3217,27 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:39</t>
+          <t>2025-12-04 18:18:53</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>24.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:39</t>
+          <t>2025-12-04 18:18:53</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>62.2</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:41</t>
+          <t>2025-12-04 18:18:55</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -3249,27 +3249,27 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:41</t>
+          <t>2025-12-04 18:18:55</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>28</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:41</t>
+          <t>2025-12-04 18:18:55</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>56.1</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:43</t>
+          <t>2025-12-04 18:18:57</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -3281,27 +3281,27 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:43</t>
+          <t>2025-12-04 18:18:57</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>26.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:43</t>
+          <t>2025-12-04 18:18:57</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>63.6</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:45</t>
+          <t>2025-12-04 18:18:59</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -3313,27 +3313,27 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:45</t>
+          <t>2025-12-04 18:18:59</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:45</t>
+          <t>2025-12-04 18:18:59</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>69.3</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:47</t>
+          <t>2025-12-04 18:19:01</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -3345,27 +3345,27 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:47</t>
+          <t>2025-12-04 18:19:01</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>26.7</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:47</t>
+          <t>2025-12-04 18:19:01</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>58.6</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:49</t>
+          <t>2025-12-04 18:19:03</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -3377,27 +3377,27 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:49</t>
+          <t>2025-12-04 18:19:03</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:49</t>
+          <t>2025-12-04 18:19:03</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>57.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:51</t>
+          <t>2025-12-04 18:19:05</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -3409,27 +3409,27 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:51</t>
+          <t>2025-12-04 18:19:05</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>29.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:51</t>
+          <t>2025-12-04 18:19:05</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>64.7</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:53</t>
+          <t>2025-12-04 18:19:07</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -3441,27 +3441,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:53</t>
+          <t>2025-12-04 18:19:07</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:53</t>
+          <t>2025-12-04 18:19:07</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>52.3</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:55</t>
+          <t>2025-12-04 18:19:09</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -3473,27 +3473,27 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:55</t>
+          <t>2025-12-04 18:19:09</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:55</t>
+          <t>2025-12-04 18:19:09</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>54.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:57</t>
+          <t>2025-12-04 18:19:11</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -3505,27 +3505,27 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:57</t>
+          <t>2025-12-04 18:19:11</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>28.6</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:57</t>
+          <t>2025-12-04 18:19:11</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>54.3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:59</t>
+          <t>2025-12-04 18:19:13</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -3537,27 +3537,27 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:59</t>
+          <t>2025-12-04 18:19:13</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>26.8</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-12-04 17:16:59</t>
+          <t>2025-12-04 18:19:13</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>65.40000000000001</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:01</t>
+          <t>2025-12-04 18:19:15</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -3569,27 +3569,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:01</t>
+          <t>2025-12-04 18:19:15</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>25.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:01</t>
+          <t>2025-12-04 18:19:15</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>51.4</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:03</t>
+          <t>2025-12-04 18:19:17</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -3601,27 +3601,27 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:03</t>
+          <t>2025-12-04 18:19:17</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>29.7</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:03</t>
+          <t>2025-12-04 18:19:17</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>57.9</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:05</t>
+          <t>2025-12-04 18:19:19</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -3633,23 +3633,23 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:05</t>
+          <t>2025-12-04 18:19:19</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>28</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-12-04 17:17:05</t>
+          <t>2025-12-04 18:19:19</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>50.1</v>
+        <v>51.6</v>
       </c>
     </row>
   </sheetData>
